--- a/dataset/Non-Faulty/improper_termination_of_block.xlsx
+++ b/dataset/Non-Faulty/improper_termination_of_block.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/improper_termination_of_block.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
